--- a/Grids Germany/No leap years/Bavaria insights/[Bavaria][Euclidean][Raw]Yearly_normality.xlsx
+++ b/Grids Germany/No leap years/Bavaria insights/[Bavaria][Euclidean][Raw]Yearly_normality.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,52 +429,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>YEAR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>n_P1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>n_P2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Shapiro_P1_W</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Shapiro_P1_p</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>P1_Normality</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Shapiro_P2_W</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Shapiro_P2_p</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>P2_Normality</t>
         </is>
@@ -478,16 +490,16 @@
         <v>1996</v>
       </c>
       <c r="C2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2" t="n">
         <v>19</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9751070141792297</v>
+        <v>0.9743357300758362</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8250662088394165</v>
+        <v>0.8257762789726257</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -516,16 +528,16 @@
         <v>1997</v>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" t="n">
         <v>19</v>
       </c>
       <c r="E3" t="n">
-        <v>0.93462073802948</v>
+        <v>0.9372853636741638</v>
       </c>
       <c r="F3" t="n">
-        <v>0.153121143579483</v>
+        <v>0.1924930065870285</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -554,16 +566,16 @@
         <v>1998</v>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D4" t="n">
         <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9670775532722473</v>
+        <v>0.9733763933181763</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6435500979423523</v>
+        <v>0.8060444593429565</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -592,16 +604,16 @@
         <v>1999</v>
       </c>
       <c r="C5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D5" t="n">
         <v>19</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9620288610458374</v>
+        <v>0.9584242105484009</v>
       </c>
       <c r="F5" t="n">
-        <v>0.531353235244751</v>
+        <v>0.4849690794944763</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -630,16 +642,16 @@
         <v>2000</v>
       </c>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
         <v>19</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9259341359138489</v>
+        <v>0.9169406294822693</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1009611934423447</v>
+        <v>0.07539383322000504</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -668,16 +680,16 @@
         <v>2001</v>
       </c>
       <c r="C7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D7" t="n">
         <v>19</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9451565742492676</v>
+        <v>0.9613901972770691</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2524420619010925</v>
+        <v>0.5445655584335327</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -706,16 +718,16 @@
         <v>2002</v>
       </c>
       <c r="C8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
         <v>19</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9530055522918701</v>
+        <v>0.9549976587295532</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3618036210536957</v>
+        <v>0.421602874994278</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -744,16 +756,16 @@
         <v>2003</v>
       </c>
       <c r="C9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D9" t="n">
         <v>19</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8732955455780029</v>
+        <v>0.8677728772163391</v>
       </c>
       <c r="F9" t="n">
-        <v>0.009020573459565639</v>
+        <v>0.008732751943171024</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -782,16 +794,16 @@
         <v>2004</v>
       </c>
       <c r="C10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D10" t="n">
         <v>19</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9693162441253662</v>
+        <v>0.9592723846435547</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6952407956123352</v>
+        <v>0.501589834690094</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -820,16 +832,16 @@
         <v>2005</v>
       </c>
       <c r="C11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11" t="n">
         <v>19</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9681968688964844</v>
+        <v>0.9387905597686768</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6693446040153503</v>
+        <v>0.2062126994132996</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -858,16 +870,16 @@
         <v>2006</v>
       </c>
       <c r="C12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D12" t="n">
         <v>19</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9460517168045044</v>
+        <v>0.9241254329681396</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2632173001766205</v>
+        <v>0.104948915541172</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -896,16 +908,16 @@
         <v>2007</v>
       </c>
       <c r="C13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D13" t="n">
         <v>19</v>
       </c>
       <c r="E13" t="n">
-        <v>0.901193380355835</v>
+        <v>0.8599658608436584</v>
       </c>
       <c r="F13" t="n">
-        <v>0.03140759468078613</v>
+        <v>0.006338227540254593</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -934,20 +946,20 @@
         <v>2008</v>
       </c>
       <c r="C14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D14" t="n">
         <v>19</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9092565774917603</v>
+        <v>0.9607800841331482</v>
       </c>
       <c r="F14" t="n">
-        <v>0.04571693390607834</v>
+        <v>0.5319792628288269</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -972,16 +984,16 @@
         <v>2009</v>
       </c>
       <c r="C15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8540027737617493</v>
+        <v>0.845057487487793</v>
       </c>
       <c r="F15" t="n">
-        <v>0.003998943604528904</v>
+        <v>0.003495634067803621</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1010,16 +1022,16 @@
         <v>2010</v>
       </c>
       <c r="C16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D16" t="n">
         <v>19</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9624761343002319</v>
+        <v>0.9737780690193176</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5408979058265686</v>
+        <v>0.8143783211708069</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1048,16 +1060,16 @@
         <v>2011</v>
       </c>
       <c r="C17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D17" t="n">
         <v>19</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9572641253471375</v>
+        <v>0.9628580212593079</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4360354244709015</v>
+        <v>0.5754627585411072</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1086,16 +1098,16 @@
         <v>2012</v>
       </c>
       <c r="C18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D18" t="n">
         <v>19</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8903644680976868</v>
+        <v>0.8289205431938171</v>
       </c>
       <c r="F18" t="n">
-        <v>0.01916201040148735</v>
+        <v>0.001880423980765045</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1124,16 +1136,16 @@
         <v>2013</v>
       </c>
       <c r="C19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D19" t="n">
         <v>19</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9639319181442261</v>
+        <v>0.9483522772789001</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5725735425949097</v>
+        <v>0.3169512450695038</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1162,16 +1174,16 @@
         <v>2014</v>
       </c>
       <c r="C20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D20" t="n">
         <v>19</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9475683569908142</v>
+        <v>0.9546504020690918</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2824307978153229</v>
+        <v>0.4155334532260895</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1200,16 +1212,16 @@
         <v>2015</v>
       </c>
       <c r="C21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D21" t="n">
         <v>19</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9605860114097595</v>
+        <v>0.9629620313644409</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5012158155441284</v>
+        <v>0.5776817798614502</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1238,16 +1250,16 @@
         <v>2016</v>
       </c>
       <c r="C22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D22" t="n">
         <v>19</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8917491436004639</v>
+        <v>0.8849518895149231</v>
       </c>
       <c r="F22" t="n">
-        <v>0.02039785124361515</v>
+        <v>0.0180676244199276</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1276,16 +1288,16 @@
         <v>2017</v>
       </c>
       <c r="C23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D23" t="n">
         <v>19</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9766151905059814</v>
+        <v>0.9731215834617615</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8557865619659424</v>
+        <v>0.8007075786590576</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1314,16 +1326,16 @@
         <v>2018</v>
       </c>
       <c r="C24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D24" t="n">
         <v>19</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9380262494087219</v>
+        <v>0.9430310726165771</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1801828891038895</v>
+        <v>0.2500011920928955</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1352,16 +1364,16 @@
         <v>2019</v>
       </c>
       <c r="C25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D25" t="n">
         <v>19</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9516631364822388</v>
+        <v>0.9428334832191467</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3406274020671844</v>
+        <v>0.2477824240922928</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1390,16 +1402,16 @@
         <v>2020</v>
       </c>
       <c r="C26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D26" t="n">
         <v>19</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7760146856307983</v>
+        <v>0.7667121291160583</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0002157726412406191</v>
+        <v>0.0002120905264746398</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1428,16 +1440,16 @@
         <v>2021</v>
       </c>
       <c r="C27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D27" t="n">
         <v>19</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9200078248977661</v>
+        <v>0.9316151142120361</v>
       </c>
       <c r="F27" t="n">
-        <v>0.07604696601629257</v>
+        <v>0.1483040601015091</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1466,16 +1478,16 @@
         <v>2022</v>
       </c>
       <c r="C28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D28" t="n">
         <v>19</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9861749410629272</v>
+        <v>0.9847608208656311</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9833042025566101</v>
+        <v>0.9767791628837585</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1504,16 +1516,16 @@
         <v>2023</v>
       </c>
       <c r="C29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D29" t="n">
         <v>19</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8881442546844482</v>
+        <v>0.8719526529312134</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01734212040901184</v>
+        <v>0.01039378810673952</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1542,16 +1554,16 @@
         <v>2024</v>
       </c>
       <c r="C30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D30" t="n">
         <v>19</v>
       </c>
       <c r="E30" t="n">
-        <v>0.887790322303772</v>
+        <v>0.8732280731201172</v>
       </c>
       <c r="F30" t="n">
-        <v>0.01706927828490734</v>
+        <v>0.01096487045288086</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1580,16 +1592,16 @@
         <v>2025</v>
       </c>
       <c r="C31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D31" t="n">
         <v>19</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9665568470954895</v>
+        <v>0.9767823219299316</v>
       </c>
       <c r="F31" t="n">
-        <v>0.6316202282905579</v>
+        <v>0.8728870153427124</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1618,16 +1630,16 @@
         <v>1996</v>
       </c>
       <c r="C32" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D32" t="n">
         <v>19</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9083369374275208</v>
+        <v>0.8992817997932434</v>
       </c>
       <c r="F32" t="n">
-        <v>0.04378772526979446</v>
+        <v>0.03388957679271698</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1656,16 +1668,16 @@
         <v>1997</v>
       </c>
       <c r="C33" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D33" t="n">
         <v>19</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9174996018409729</v>
+        <v>0.9359908699989319</v>
       </c>
       <c r="F33" t="n">
-        <v>0.06748612970113754</v>
+        <v>0.1813981086015701</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1694,16 +1706,16 @@
         <v>1998</v>
       </c>
       <c r="C34" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D34" t="n">
         <v>19</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9392371773719788</v>
+        <v>0.9412600994110107</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1908803582191467</v>
+        <v>0.2307512164115906</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1732,16 +1744,16 @@
         <v>1999</v>
       </c>
       <c r="C35" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D35" t="n">
         <v>19</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9658277034759521</v>
+        <v>0.9744341373443604</v>
       </c>
       <c r="F35" t="n">
-        <v>0.6150138378143311</v>
+        <v>0.8277643918991089</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1770,16 +1782,16 @@
         <v>2000</v>
       </c>
       <c r="C36" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D36" t="n">
         <v>19</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9691305160522461</v>
+        <v>0.9685105681419373</v>
       </c>
       <c r="F36" t="n">
-        <v>0.690942645072937</v>
+        <v>0.6998835206031799</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1808,16 +1820,16 @@
         <v>2001</v>
       </c>
       <c r="C37" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D37" t="n">
         <v>19</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9726942777633667</v>
+        <v>0.9570712447166443</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7725487947463989</v>
+        <v>0.4592090547084808</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1846,16 +1858,16 @@
         <v>2002</v>
       </c>
       <c r="C38" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D38" t="n">
         <v>19</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9717795848846436</v>
+        <v>0.9639765024185181</v>
       </c>
       <c r="F38" t="n">
-        <v>0.751891553401947</v>
+        <v>0.5995233058929443</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1884,16 +1896,16 @@
         <v>2003</v>
       </c>
       <c r="C39" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D39" t="n">
         <v>19</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9729771614074707</v>
+        <v>0.9745261073112488</v>
       </c>
       <c r="F39" t="n">
-        <v>0.7788695096969604</v>
+        <v>0.829617440700531</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1922,16 +1934,16 @@
         <v>2004</v>
       </c>
       <c r="C40" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D40" t="n">
         <v>19</v>
       </c>
       <c r="E40" t="n">
-        <v>0.962612509727478</v>
+        <v>0.9374935626983643</v>
       </c>
       <c r="F40" t="n">
-        <v>0.543826699256897</v>
+        <v>0.1943372637033463</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1960,16 +1972,16 @@
         <v>2005</v>
       </c>
       <c r="C41" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D41" t="n">
         <v>19</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9306694269180298</v>
+        <v>0.9340894222259521</v>
       </c>
       <c r="F41" t="n">
-        <v>0.126700684428215</v>
+        <v>0.1662150621414185</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1998,16 +2010,16 @@
         <v>2006</v>
       </c>
       <c r="C42" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D42" t="n">
         <v>19</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9439069628715515</v>
+        <v>0.9419907331466675</v>
       </c>
       <c r="F42" t="n">
-        <v>0.2380751371383667</v>
+        <v>0.2385199666023254</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2036,16 +2048,16 @@
         <v>2007</v>
       </c>
       <c r="C43" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D43" t="n">
         <v>19</v>
       </c>
       <c r="E43" t="n">
-        <v>0.9488094449043274</v>
+        <v>0.9552140235900879</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2990752160549164</v>
+        <v>0.4254183769226074</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2074,16 +2086,16 @@
         <v>2008</v>
       </c>
       <c r="C44" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D44" t="n">
         <v>19</v>
       </c>
       <c r="E44" t="n">
-        <v>0.96652752161026</v>
+        <v>0.9672336578369141</v>
       </c>
       <c r="F44" t="n">
-        <v>0.630949854850769</v>
+        <v>0.6713722944259644</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2112,16 +2124,16 @@
         <v>2009</v>
       </c>
       <c r="C45" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D45" t="n">
         <v>19</v>
       </c>
       <c r="E45" t="n">
-        <v>0.8851914405822754</v>
+        <v>0.8947228789329529</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0151992766186595</v>
+        <v>0.02768442220985889</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2150,16 +2162,16 @@
         <v>2010</v>
       </c>
       <c r="C46" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D46" t="n">
         <v>19</v>
       </c>
       <c r="E46" t="n">
-        <v>0.9332311153411865</v>
+        <v>0.9322137832641602</v>
       </c>
       <c r="F46" t="n">
-        <v>0.1432600021362305</v>
+        <v>0.152455672621727</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2188,16 +2200,16 @@
         <v>2011</v>
       </c>
       <c r="C47" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D47" t="n">
         <v>19</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9090568423271179</v>
+        <v>0.9035637378692627</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0452904999256134</v>
+        <v>0.0410488061606884</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2226,16 +2238,16 @@
         <v>2012</v>
       </c>
       <c r="C48" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D48" t="n">
         <v>19</v>
       </c>
       <c r="E48" t="n">
-        <v>0.9467598795890808</v>
+        <v>0.9093924760818481</v>
       </c>
       <c r="F48" t="n">
-        <v>0.2720373868942261</v>
+        <v>0.05341550335288048</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2264,16 +2276,16 @@
         <v>2013</v>
       </c>
       <c r="C49" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D49" t="n">
         <v>19</v>
       </c>
       <c r="E49" t="n">
-        <v>0.9196430444717407</v>
+        <v>0.9132412075996399</v>
       </c>
       <c r="F49" t="n">
-        <v>0.07473574578762054</v>
+        <v>0.06364813446998596</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2302,16 +2314,16 @@
         <v>2014</v>
       </c>
       <c r="C50" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D50" t="n">
         <v>19</v>
       </c>
       <c r="E50" t="n">
-        <v>0.9842554330825806</v>
+        <v>0.9680543541908264</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9688192009925842</v>
+        <v>0.6896951198577881</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2340,16 +2352,16 @@
         <v>2015</v>
       </c>
       <c r="C51" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D51" t="n">
         <v>19</v>
       </c>
       <c r="E51" t="n">
-        <v>0.9563661813735962</v>
+        <v>0.978940486907959</v>
       </c>
       <c r="F51" t="n">
-        <v>0.4194928705692291</v>
+        <v>0.9094510078430176</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2378,16 +2390,16 @@
         <v>2016</v>
       </c>
       <c r="C52" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D52" t="n">
         <v>19</v>
       </c>
       <c r="E52" t="n">
-        <v>0.9151734113693237</v>
+        <v>0.9258299469947815</v>
       </c>
       <c r="F52" t="n">
-        <v>0.06043168902397156</v>
+        <v>0.1135408133268356</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2416,16 +2428,16 @@
         <v>2017</v>
       </c>
       <c r="C53" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D53" t="n">
         <v>19</v>
       </c>
       <c r="E53" t="n">
-        <v>0.8911020159721375</v>
+        <v>0.9002159237861633</v>
       </c>
       <c r="F53" t="n">
-        <v>0.01981017179787159</v>
+        <v>0.03533164784312248</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2454,16 +2466,16 @@
         <v>2018</v>
       </c>
       <c r="C54" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D54" t="n">
         <v>19</v>
       </c>
       <c r="E54" t="n">
-        <v>0.9505472779273987</v>
+        <v>0.9558091759681702</v>
       </c>
       <c r="F54" t="n">
-        <v>0.3238246142864227</v>
+        <v>0.4360448122024536</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2492,16 +2504,16 @@
         <v>2019</v>
       </c>
       <c r="C55" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D55" t="n">
         <v>19</v>
       </c>
       <c r="E55" t="n">
-        <v>0.916965663433075</v>
+        <v>0.9234060049057007</v>
       </c>
       <c r="F55" t="n">
-        <v>0.06579525023698807</v>
+        <v>0.1015224978327751</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2530,20 +2542,20 @@
         <v>2020</v>
       </c>
       <c r="C56" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D56" t="n">
         <v>19</v>
       </c>
       <c r="E56" t="n">
-        <v>0.8990290760993958</v>
+        <v>0.9211708307266235</v>
       </c>
       <c r="F56" t="n">
-        <v>0.02842684462666512</v>
+        <v>0.0915820375084877</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H56" t="n">
@@ -2568,16 +2580,16 @@
         <v>2021</v>
       </c>
       <c r="C57" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D57" t="n">
         <v>19</v>
       </c>
       <c r="E57" t="n">
-        <v>0.944177508354187</v>
+        <v>0.9330516457557678</v>
       </c>
       <c r="F57" t="n">
-        <v>0.2411197423934937</v>
+        <v>0.158458411693573</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2606,16 +2618,16 @@
         <v>2022</v>
       </c>
       <c r="C58" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D58" t="n">
         <v>19</v>
       </c>
       <c r="E58" t="n">
-        <v>0.9522525668144226</v>
+        <v>0.9483745098114014</v>
       </c>
       <c r="F58" t="n">
-        <v>0.3497946262359619</v>
+        <v>0.3172615468502045</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2644,16 +2656,16 @@
         <v>2023</v>
       </c>
       <c r="C59" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D59" t="n">
         <v>19</v>
       </c>
       <c r="E59" t="n">
-        <v>0.9343225359916687</v>
+        <v>0.9317252635955811</v>
       </c>
       <c r="F59" t="n">
-        <v>0.1509501188993454</v>
+        <v>0.1490592956542969</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2682,16 +2694,16 @@
         <v>2024</v>
       </c>
       <c r="C60" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D60" t="n">
         <v>19</v>
       </c>
       <c r="E60" t="n">
-        <v>0.9587284922599792</v>
+        <v>0.9667004942893982</v>
       </c>
       <c r="F60" t="n">
-        <v>0.464012622833252</v>
+        <v>0.6594910621643066</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2720,16 +2732,16 @@
         <v>2025</v>
       </c>
       <c r="C61" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D61" t="n">
         <v>19</v>
       </c>
       <c r="E61" t="n">
-        <v>0.9332985877990723</v>
+        <v>0.9366802573204041</v>
       </c>
       <c r="F61" t="n">
-        <v>0.1437240242958069</v>
+        <v>0.1872279345989227</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2758,16 +2770,16 @@
         <v>1996</v>
       </c>
       <c r="C62" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D62" t="n">
         <v>19</v>
       </c>
       <c r="E62" t="n">
-        <v>0.903363823890686</v>
+        <v>0.8966967463493347</v>
       </c>
       <c r="F62" t="n">
-        <v>0.0347265899181366</v>
+        <v>0.03021067753434181</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2796,16 +2808,16 @@
         <v>1997</v>
       </c>
       <c r="C63" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D63" t="n">
         <v>19</v>
       </c>
       <c r="E63" t="n">
-        <v>0.9552439451217651</v>
+        <v>0.9584916830062866</v>
       </c>
       <c r="F63" t="n">
-        <v>0.3994830846786499</v>
+        <v>0.4862786829471588</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2834,16 +2846,16 @@
         <v>1998</v>
       </c>
       <c r="C64" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D64" t="n">
         <v>19</v>
       </c>
       <c r="E64" t="n">
-        <v>0.9565116763114929</v>
+        <v>0.9547099471092224</v>
       </c>
       <c r="F64" t="n">
-        <v>0.4221411347389221</v>
+        <v>0.4165686964988708</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2872,20 +2884,20 @@
         <v>1999</v>
       </c>
       <c r="C65" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D65" t="n">
         <v>19</v>
       </c>
       <c r="E65" t="n">
-        <v>0.8894153237342834</v>
+        <v>0.9428867697715759</v>
       </c>
       <c r="F65" t="n">
-        <v>0.01836057007312775</v>
+        <v>0.2483785450458527</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H65" t="n">
@@ -2910,16 +2922,16 @@
         <v>2000</v>
       </c>
       <c r="C66" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D66" t="n">
         <v>19</v>
       </c>
       <c r="E66" t="n">
-        <v>0.9657432436943054</v>
+        <v>0.9599401354789734</v>
       </c>
       <c r="F66" t="n">
-        <v>0.6131000518798828</v>
+        <v>0.5149192810058594</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2948,16 +2960,16 @@
         <v>2001</v>
       </c>
       <c r="C67" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D67" t="n">
         <v>19</v>
       </c>
       <c r="E67" t="n">
-        <v>0.9749055504798889</v>
+        <v>0.9373108148574829</v>
       </c>
       <c r="F67" t="n">
-        <v>0.8208220601081848</v>
+        <v>0.1927177608013153</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2986,16 +2998,16 @@
         <v>2002</v>
       </c>
       <c r="C68" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D68" t="n">
         <v>19</v>
       </c>
       <c r="E68" t="n">
-        <v>0.9527192711830139</v>
+        <v>0.9549463391304016</v>
       </c>
       <c r="F68" t="n">
-        <v>0.3571987152099609</v>
+        <v>0.4207023084163666</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3024,16 +3036,16 @@
         <v>2003</v>
       </c>
       <c r="C69" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D69" t="n">
         <v>19</v>
       </c>
       <c r="E69" t="n">
-        <v>0.8589954972267151</v>
+        <v>0.8424633145332336</v>
       </c>
       <c r="F69" t="n">
-        <v>0.004917121026664972</v>
+        <v>0.003158775856718421</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3062,16 +3074,16 @@
         <v>2004</v>
       </c>
       <c r="C70" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D70" t="n">
         <v>19</v>
       </c>
       <c r="E70" t="n">
-        <v>0.9805152416229248</v>
+        <v>0.9723951816558838</v>
       </c>
       <c r="F70" t="n">
-        <v>0.9238624572753906</v>
+        <v>0.7853063344955444</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3100,16 +3112,16 @@
         <v>2005</v>
       </c>
       <c r="C71" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D71" t="n">
         <v>19</v>
       </c>
       <c r="E71" t="n">
-        <v>0.9687264561653137</v>
+        <v>0.9701550602912903</v>
       </c>
       <c r="F71" t="n">
-        <v>0.6815921664237976</v>
+        <v>0.7364707589149475</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3138,20 +3150,20 @@
         <v>2006</v>
       </c>
       <c r="C72" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D72" t="n">
         <v>19</v>
       </c>
       <c r="E72" t="n">
-        <v>0.9265779852867126</v>
+        <v>0.8989871144294739</v>
       </c>
       <c r="F72" t="n">
-        <v>0.1041253581643105</v>
+        <v>0.03344747051596642</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
       <c r="H72" t="n">
@@ -3176,16 +3188,16 @@
         <v>2007</v>
       </c>
       <c r="C73" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D73" t="n">
         <v>19</v>
       </c>
       <c r="E73" t="n">
-        <v>0.9503281712532043</v>
+        <v>0.9475137591362</v>
       </c>
       <c r="F73" t="n">
-        <v>0.3206103146076202</v>
+        <v>0.3054462075233459</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3214,16 +3226,16 @@
         <v>2008</v>
       </c>
       <c r="C74" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D74" t="n">
         <v>19</v>
       </c>
       <c r="E74" t="n">
-        <v>0.9678798913955688</v>
+        <v>0.9734296798706055</v>
       </c>
       <c r="F74" t="n">
-        <v>0.662024199962616</v>
+        <v>0.8071550130844116</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3252,16 +3264,16 @@
         <v>2009</v>
       </c>
       <c r="C75" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D75" t="n">
         <v>19</v>
       </c>
       <c r="E75" t="n">
-        <v>0.9525855779647827</v>
+        <v>0.9616391658782959</v>
       </c>
       <c r="F75" t="n">
-        <v>0.3550649881362915</v>
+        <v>0.5497466921806335</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3290,16 +3302,16 @@
         <v>2010</v>
       </c>
       <c r="C76" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D76" t="n">
         <v>19</v>
       </c>
       <c r="E76" t="n">
-        <v>0.9774510860443115</v>
+        <v>0.9780640602111816</v>
       </c>
       <c r="F76" t="n">
-        <v>0.8718934059143066</v>
+        <v>0.8952515721321106</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3328,16 +3340,16 @@
         <v>2011</v>
       </c>
       <c r="C77" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D77" t="n">
         <v>19</v>
       </c>
       <c r="E77" t="n">
-        <v>0.9282993674278259</v>
+        <v>0.9141294360160828</v>
       </c>
       <c r="F77" t="n">
-        <v>0.1130848303437233</v>
+        <v>0.06628472357988358</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3366,20 +3378,20 @@
         <v>2012</v>
       </c>
       <c r="C78" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D78" t="n">
         <v>19</v>
       </c>
       <c r="E78" t="n">
-        <v>0.8874314427375793</v>
+        <v>0.9167885184288025</v>
       </c>
       <c r="F78" t="n">
-        <v>0.01679724641144276</v>
+        <v>0.07486972957849503</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H78" t="n">
@@ -3404,16 +3416,16 @@
         <v>2013</v>
       </c>
       <c r="C79" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D79" t="n">
         <v>19</v>
       </c>
       <c r="E79" t="n">
-        <v>0.97437584400177</v>
+        <v>0.9776308536529541</v>
       </c>
       <c r="F79" t="n">
-        <v>0.8095244765281677</v>
+        <v>0.8878955841064453</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3442,16 +3454,16 @@
         <v>2014</v>
       </c>
       <c r="C80" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D80" t="n">
         <v>19</v>
       </c>
       <c r="E80" t="n">
-        <v>0.8830855488777161</v>
+        <v>0.8876141905784607</v>
       </c>
       <c r="F80" t="n">
-        <v>0.01384271495044231</v>
+        <v>0.02027660794556141</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3480,16 +3492,16 @@
         <v>2015</v>
       </c>
       <c r="C81" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D81" t="n">
         <v>19</v>
       </c>
       <c r="E81" t="n">
-        <v>0.9289203882217407</v>
+        <v>0.9387403726577759</v>
       </c>
       <c r="F81" t="n">
-        <v>0.1165041550993919</v>
+        <v>0.2057405263185501</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3518,16 +3530,16 @@
         <v>2016</v>
       </c>
       <c r="C82" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D82" t="n">
         <v>19</v>
       </c>
       <c r="E82" t="n">
-        <v>0.9657801389694214</v>
+        <v>0.9627894163131714</v>
       </c>
       <c r="F82" t="n">
-        <v>0.6139357089996338</v>
+        <v>0.5740002393722534</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3556,16 +3568,16 @@
         <v>2017</v>
       </c>
       <c r="C83" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D83" t="n">
         <v>19</v>
       </c>
       <c r="E83" t="n">
-        <v>0.8645221590995789</v>
+        <v>0.8408233523368835</v>
       </c>
       <c r="F83" t="n">
-        <v>0.006200398318469524</v>
+        <v>0.002963756211102009</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3594,16 +3606,16 @@
         <v>2018</v>
       </c>
       <c r="C84" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D84" t="n">
         <v>19</v>
       </c>
       <c r="E84" t="n">
-        <v>0.8915978074073792</v>
+        <v>0.8916608095169067</v>
       </c>
       <c r="F84" t="n">
-        <v>0.02025882713496685</v>
+        <v>0.02419463358819485</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3632,16 +3644,16 @@
         <v>2019</v>
       </c>
       <c r="C85" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D85" t="n">
         <v>19</v>
       </c>
       <c r="E85" t="n">
-        <v>0.9583404660224915</v>
+        <v>0.9594167470932007</v>
       </c>
       <c r="F85" t="n">
-        <v>0.4564798176288605</v>
+        <v>0.5044535398483276</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -3670,16 +3682,16 @@
         <v>2020</v>
       </c>
       <c r="C86" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D86" t="n">
         <v>19</v>
       </c>
       <c r="E86" t="n">
-        <v>0.8444902896881104</v>
+        <v>0.8649210929870605</v>
       </c>
       <c r="F86" t="n">
-        <v>0.002716696355491877</v>
+        <v>0.007762450259178877</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -3708,16 +3720,16 @@
         <v>2021</v>
       </c>
       <c r="C87" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D87" t="n">
         <v>19</v>
       </c>
       <c r="E87" t="n">
-        <v>0.9094638824462891</v>
+        <v>0.898874044418335</v>
       </c>
       <c r="F87" t="n">
-        <v>0.04616379737854004</v>
+        <v>0.03327945992350578</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -3746,16 +3758,16 @@
         <v>2022</v>
       </c>
       <c r="C88" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D88" t="n">
         <v>19</v>
       </c>
       <c r="E88" t="n">
-        <v>0.9616022706031799</v>
+        <v>0.9574477672576904</v>
       </c>
       <c r="F88" t="n">
-        <v>0.5223360061645508</v>
+        <v>0.4662835001945496</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -3784,16 +3796,16 @@
         <v>2023</v>
       </c>
       <c r="C89" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D89" t="n">
         <v>19</v>
       </c>
       <c r="E89" t="n">
-        <v>0.961011528968811</v>
+        <v>0.9373272657394409</v>
       </c>
       <c r="F89" t="n">
-        <v>0.5099961161613464</v>
+        <v>0.1928630620241165</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -3822,16 +3834,16 @@
         <v>2024</v>
       </c>
       <c r="C90" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D90" t="n">
         <v>19</v>
       </c>
       <c r="E90" t="n">
-        <v>0.9258203506469727</v>
+        <v>0.9344719648361206</v>
       </c>
       <c r="F90" t="n">
-        <v>0.1004122570157051</v>
+        <v>0.1691668033599854</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -3860,16 +3872,16 @@
         <v>2025</v>
       </c>
       <c r="C91" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D91" t="n">
         <v>19</v>
       </c>
       <c r="E91" t="n">
-        <v>0.8743209838867188</v>
+        <v>0.8970590829849243</v>
       </c>
       <c r="F91" t="n">
-        <v>0.009429795667529106</v>
+        <v>0.03070013225078583</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -3898,16 +3910,16 @@
         <v>1996</v>
       </c>
       <c r="C92" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D92" t="n">
         <v>19</v>
       </c>
       <c r="E92" t="n">
-        <v>0.9552503824234009</v>
+        <v>0.942700207233429</v>
       </c>
       <c r="F92" t="n">
-        <v>0.3995964229106903</v>
+        <v>0.2462952733039856</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -3936,16 +3948,16 @@
         <v>1997</v>
       </c>
       <c r="C93" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D93" t="n">
         <v>19</v>
       </c>
       <c r="E93" t="n">
-        <v>0.9566518068313599</v>
+        <v>0.9461807608604431</v>
       </c>
       <c r="F93" t="n">
-        <v>0.4247032999992371</v>
+        <v>0.2879087924957275</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -3974,16 +3986,16 @@
         <v>1998</v>
       </c>
       <c r="C94" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D94" t="n">
         <v>19</v>
       </c>
       <c r="E94" t="n">
-        <v>0.9235408306121826</v>
+        <v>0.9370284080505371</v>
       </c>
       <c r="F94" t="n">
-        <v>0.09002842754125595</v>
+        <v>0.190240204334259</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -4012,16 +4024,16 @@
         <v>1999</v>
       </c>
       <c r="C95" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D95" t="n">
         <v>19</v>
       </c>
       <c r="E95" t="n">
-        <v>0.9418253302574158</v>
+        <v>0.9445294737815857</v>
       </c>
       <c r="F95" t="n">
-        <v>0.2158181220293045</v>
+        <v>0.2674317061901093</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -4050,16 +4062,16 @@
         <v>2000</v>
       </c>
       <c r="C96" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D96" t="n">
         <v>19</v>
       </c>
       <c r="E96" t="n">
-        <v>0.9135215878486633</v>
+        <v>0.9169558882713318</v>
       </c>
       <c r="F96" t="n">
-        <v>0.05588743090629578</v>
+        <v>0.07544665783643723</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -4088,16 +4100,16 @@
         <v>2001</v>
       </c>
       <c r="C97" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D97" t="n">
         <v>19</v>
       </c>
       <c r="E97" t="n">
-        <v>0.9400941729545593</v>
+        <v>0.9504258036613464</v>
       </c>
       <c r="F97" t="n">
-        <v>0.1988168805837631</v>
+        <v>0.3470108211040497</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -4126,16 +4138,16 @@
         <v>2002</v>
       </c>
       <c r="C98" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D98" t="n">
         <v>19</v>
       </c>
       <c r="E98" t="n">
-        <v>0.9369547963142395</v>
+        <v>0.9603297710418701</v>
       </c>
       <c r="F98" t="n">
-        <v>0.1712021678686142</v>
+        <v>0.5227931141853333</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -4164,16 +4176,16 @@
         <v>2003</v>
       </c>
       <c r="C99" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D99" t="n">
         <v>19</v>
       </c>
       <c r="E99" t="n">
-        <v>0.8798585534095764</v>
+        <v>0.8816277980804443</v>
       </c>
       <c r="F99" t="n">
-        <v>0.01200640015304089</v>
+        <v>0.01565987803041935</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -4202,16 +4214,16 @@
         <v>2004</v>
       </c>
       <c r="C100" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D100" t="n">
         <v>19</v>
       </c>
       <c r="E100" t="n">
-        <v>0.9515150189399719</v>
+        <v>0.9555971622467041</v>
       </c>
       <c r="F100" t="n">
-        <v>0.3383555114269257</v>
+        <v>0.4322375059127808</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -4240,16 +4252,16 @@
         <v>2005</v>
       </c>
       <c r="C101" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D101" t="n">
         <v>19</v>
       </c>
       <c r="E101" t="n">
-        <v>0.9760701060295105</v>
+        <v>0.9374268054962158</v>
       </c>
       <c r="F101" t="n">
-        <v>0.8449122309684753</v>
+        <v>0.1937442272901535</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -4278,16 +4290,16 @@
         <v>2006</v>
       </c>
       <c r="C102" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D102" t="n">
         <v>19</v>
       </c>
       <c r="E102" t="n">
-        <v>0.9554104804992676</v>
+        <v>0.9446125030517578</v>
       </c>
       <c r="F102" t="n">
-        <v>0.4024056494235992</v>
+        <v>0.2684287130832672</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -4316,16 +4328,16 @@
         <v>2007</v>
       </c>
       <c r="C103" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D103" t="n">
         <v>19</v>
       </c>
       <c r="E103" t="n">
-        <v>0.9468004703521729</v>
+        <v>0.9693787097930908</v>
       </c>
       <c r="F103" t="n">
-        <v>0.2725505530834198</v>
+        <v>0.7192398309707642</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -4354,16 +4366,16 @@
         <v>2008</v>
       </c>
       <c r="C104" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D104" t="n">
         <v>19</v>
       </c>
       <c r="E104" t="n">
-        <v>0.9884957075119019</v>
+        <v>0.9618595838546753</v>
       </c>
       <c r="F104" t="n">
-        <v>0.9937896728515625</v>
+        <v>0.5543541312217712</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -4392,16 +4404,16 @@
         <v>2009</v>
       </c>
       <c r="C105" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D105" t="n">
         <v>19</v>
       </c>
       <c r="E105" t="n">
-        <v>0.8254415988922119</v>
+        <v>0.8080654144287109</v>
       </c>
       <c r="F105" t="n">
-        <v>0.001287218765355647</v>
+        <v>0.0008737375610508025</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -4430,16 +4442,16 @@
         <v>2010</v>
       </c>
       <c r="C106" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D106" t="n">
         <v>19</v>
       </c>
       <c r="E106" t="n">
-        <v>0.9568899273872375</v>
+        <v>0.966099739074707</v>
       </c>
       <c r="F106" t="n">
-        <v>0.4290844202041626</v>
+        <v>0.6461425423622131</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -4468,16 +4480,16 @@
         <v>2011</v>
       </c>
       <c r="C107" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D107" t="n">
         <v>19</v>
       </c>
       <c r="E107" t="n">
-        <v>0.9363498687744141</v>
+        <v>0.9423785209655762</v>
       </c>
       <c r="F107" t="n">
-        <v>0.1663249582052231</v>
+        <v>0.242741733789444</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -4506,16 +4518,16 @@
         <v>2012</v>
       </c>
       <c r="C108" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D108" t="n">
         <v>19</v>
       </c>
       <c r="E108" t="n">
-        <v>0.8804751038551331</v>
+        <v>0.8531951308250427</v>
       </c>
       <c r="F108" t="n">
-        <v>0.01233628112822771</v>
+        <v>0.004824069328606129</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -4544,16 +4556,16 @@
         <v>2013</v>
       </c>
       <c r="C109" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D109" t="n">
         <v>19</v>
       </c>
       <c r="E109" t="n">
-        <v>0.9534507393836975</v>
+        <v>0.9451625347137451</v>
       </c>
       <c r="F109" t="n">
-        <v>0.3690611124038696</v>
+        <v>0.2751215398311615</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -4582,16 +4594,16 @@
         <v>2014</v>
       </c>
       <c r="C110" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D110" t="n">
         <v>19</v>
       </c>
       <c r="E110" t="n">
-        <v>0.9663969874382019</v>
+        <v>0.9670591950416565</v>
       </c>
       <c r="F110" t="n">
-        <v>0.627968966960907</v>
+        <v>0.667481541633606</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -4620,16 +4632,16 @@
         <v>2015</v>
       </c>
       <c r="C111" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D111" t="n">
         <v>19</v>
       </c>
       <c r="E111" t="n">
-        <v>0.9641609787940979</v>
+        <v>0.9670847654342651</v>
       </c>
       <c r="F111" t="n">
-        <v>0.577636182308197</v>
+        <v>0.6680516004562378</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -4658,16 +4670,16 @@
         <v>2016</v>
       </c>
       <c r="C112" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D112" t="n">
         <v>19</v>
       </c>
       <c r="E112" t="n">
-        <v>0.9585829973220825</v>
+        <v>0.9606698751449585</v>
       </c>
       <c r="F112" t="n">
-        <v>0.4611778855323792</v>
+        <v>0.5297225713729858</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -4696,16 +4708,16 @@
         <v>2017</v>
       </c>
       <c r="C113" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D113" t="n">
         <v>19</v>
       </c>
       <c r="E113" t="n">
-        <v>0.9581987857818604</v>
+        <v>0.950736939907074</v>
       </c>
       <c r="F113" t="n">
-        <v>0.4537506401538849</v>
+        <v>0.3517227172851562</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -4734,16 +4746,16 @@
         <v>2018</v>
       </c>
       <c r="C114" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D114" t="n">
         <v>19</v>
       </c>
       <c r="E114" t="n">
-        <v>0.9250615835189819</v>
+        <v>0.9302734136581421</v>
       </c>
       <c r="F114" t="n">
-        <v>0.09682752192020416</v>
+        <v>0.1394009739160538</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -4772,16 +4784,16 @@
         <v>2019</v>
       </c>
       <c r="C115" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D115" t="n">
         <v>19</v>
       </c>
       <c r="E115" t="n">
-        <v>0.9594524502754211</v>
+        <v>0.9534580707550049</v>
       </c>
       <c r="F115" t="n">
-        <v>0.4782902300357819</v>
+        <v>0.3951966762542725</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -4810,16 +4822,16 @@
         <v>2020</v>
       </c>
       <c r="C116" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D116" t="n">
         <v>19</v>
       </c>
       <c r="E116" t="n">
-        <v>0.8947821855545044</v>
+        <v>0.861539900302887</v>
       </c>
       <c r="F116" t="n">
-        <v>0.02340719476342201</v>
+        <v>0.006757939700037241</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -4848,16 +4860,16 @@
         <v>2021</v>
       </c>
       <c r="C117" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D117" t="n">
         <v>19</v>
       </c>
       <c r="E117" t="n">
-        <v>0.8914653658866882</v>
+        <v>0.8977106213569641</v>
       </c>
       <c r="F117" t="n">
-        <v>0.02013794891536236</v>
+        <v>0.03160114213824272</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -4886,16 +4898,16 @@
         <v>2022</v>
       </c>
       <c r="C118" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D118" t="n">
         <v>19</v>
       </c>
       <c r="E118" t="n">
-        <v>0.9364250898361206</v>
+        <v>0.9150348901748657</v>
       </c>
       <c r="F118" t="n">
-        <v>0.1669242233037949</v>
+        <v>0.06908836215734482</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -4924,16 +4936,16 @@
         <v>2023</v>
       </c>
       <c r="C119" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D119" t="n">
         <v>19</v>
       </c>
       <c r="E119" t="n">
-        <v>0.9034411907196045</v>
+        <v>0.90504390001297</v>
       </c>
       <c r="F119" t="n">
-        <v>0.0348515659570694</v>
+        <v>0.04387648031115532</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -4962,16 +4974,16 @@
         <v>2024</v>
       </c>
       <c r="C120" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D120" t="n">
         <v>19</v>
       </c>
       <c r="E120" t="n">
-        <v>0.8783071637153625</v>
+        <v>0.8875086307525635</v>
       </c>
       <c r="F120" t="n">
-        <v>0.01121694035828114</v>
+        <v>0.02018378861248493</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -5000,16 +5012,16 @@
         <v>2025</v>
       </c>
       <c r="C121" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D121" t="n">
         <v>19</v>
       </c>
       <c r="E121" t="n">
-        <v>0.9744634032249451</v>
+        <v>0.9649559259414673</v>
       </c>
       <c r="F121" t="n">
-        <v>0.8114057779312134</v>
+        <v>0.6208981871604919</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
